--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/region-del-libertador-general-bernardo-o-higgins.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/region-del-libertador-general-bernardo-o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3690-213-CM26</t>
+          <t>3014-31-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>69.081.600-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>I MUNICIPALIDAD DE COINCO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.449.580-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>14779.8</v>
+        <v>35985.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3946-315-CM26</t>
+          <t>3863-28-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1377.31</v>
+        <v>20728.04</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1529-215-CM26</t>
+          <t>3016-31-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>69.090.500-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>I MUNICIPALIDAD DE LOLOL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>30771.02</v>
+        <v>9411.709999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3997-306-CM26</t>
+          <t>4732-31-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,6 +752,1409 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
+        <v>11540.62</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2677-59-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69.080.500-6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>36175.52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>522-29-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>61.602.152-4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hospital de Litueche</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>2663.22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1622-359-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.602.141-9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Netsus SpA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>929.15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3810-781-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.091.200-7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>9496.200000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3863-170-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.090.600-7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>14594.23</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>557639-754-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>71.014.200-9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>4441.72</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3997-246-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.080.700-9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>13316.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3864-158-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.090.600-7</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>18472.61</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3996-269-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.080.700-9</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>7545.79</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4139-176-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.091.000-4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PALMILLA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>13554.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3731-137-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.090.300-8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Netsus SpA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>7259</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1529-294-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.602.140-0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>12315.07</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3863-333-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.090.600-7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>8460.42</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2678-150-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.080.500-6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>4882.57</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3864-263-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.090.600-7</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>14803.24</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1223542-306-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>65.104.928-8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>1480.32</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3863-347-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.090.600-7</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>1480.57</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3863-431-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.090.600-7</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>3806.55</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1223542-332-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>65.104.928-8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>1480.24</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3690-213-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69.080.800-5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Inversiones Hebo Limitada</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>14779.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1529-215-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.602.140-0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>30771.02</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3946-315-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.081.100-6</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Netsus SpA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>1377.31</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3997-306-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.080.700-9</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
         <v>14635.93</v>
       </c>
     </row>
